--- a/exports/colleges/25455_iit-delhi-indian-institute-of-technology-iitd-new-delhi.xlsx
+++ b/exports/colleges/25455_iit-delhi-indian-institute-of-technology-iitd-new-delhi.xlsx
@@ -433,7 +433,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="253" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="165" customWidth="1" min="13" max="13"/>
@@ -558,7 +558,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>#1</t>
+          <t>CD Rank #1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -6750,7 +6750,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -6789,12 +6789,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2025</v>
-      </c>
+          <t>CD Rank #1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/exports/colleges/25455_iit-delhi-indian-institute-of-technology-iitd-new-delhi.xlsx
+++ b/exports/colleges/25455_iit-delhi-indian-institute-of-technology-iitd-new-delhi.xlsx
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -604,7 +604,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="35" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
@@ -685,12 +685,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 60% + GATE</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>GATE, COAP</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -742,27 +742,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vlsi Design</t>
+          <t>Bachelor of Technology [B.Tech]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vlsi Design</t>
+          <t>Bachelor of Technology [B.Tech]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 75% + JEE Advanced</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Main, JEE Advanced</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -804,22 +804,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>2.36 Lakhs</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 55% + IIT JAM</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>IIT JAM, JOAPS</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -866,27 +866,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Computer Technology</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Computer Technology</t>
+          <t>M.Phil/Ph.D in Engineering</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Post Graduation with 60%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -928,22 +928,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Construction Engineering And Management</t>
+          <t>Master of Science [M.S]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Construction Engineering And Management</t>
+          <t>Master of Science [M.S]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 60% + GATE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>GATE, IIT JAM, COAP, JOAPS</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Biomedical Engineering</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Biomedical Engineering</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Environmental Engineering</t>
+          <t>Vlsi Design</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Environmental Engineering</t>
+          <t>Vlsi Design</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mechanical Design</t>
+          <t>Cyber Security</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mechanical Design</t>
+          <t>Cyber Security</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Textile Technology</t>
+          <t>Computer Technology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Textile Technology</t>
+          <t>Computer Technology</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Power Electronics &amp; Machine Drives</t>
+          <t>Construction Engineering And Management</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Power Electronics &amp; Machine Drives</t>
+          <t>Construction Engineering And Management</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Integrated Circuit Technology</t>
+          <t>Biomedical Engineering</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Integrated Circuit Technology</t>
+          <t>Biomedical Engineering</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Instrumentation</t>
+          <t>Environmental Engineering</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Instrumentation</t>
+          <t>Environmental Engineering</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Material Science And Engineering</t>
+          <t>Mechanical Design</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Material Science And Engineering</t>
+          <t>Mechanical Design</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Textile Technology</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Textile Technology</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1553,12 +1553,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Electric Mobility</t>
+          <t>Power Electronics &amp; Machine Drives</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Electric Mobility</t>
+          <t>Power Electronics &amp; Machine Drives</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Structural Engineering</t>
+          <t>Integrated Circuit Technology</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Structural Engineering</t>
+          <t>Integrated Circuit Technology</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Polymer Science and Technology</t>
+          <t>Instrumentation</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Polymer Science and Technology</t>
+          <t>Instrumentation</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Optoelectronics And Optical Communication</t>
+          <t>Material Science And Engineering</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Optoelectronics And Optical Communication</t>
+          <t>Material Science And Engineering</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Water Resources Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Water Resources Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Control &amp; Automation</t>
+          <t>Electric Mobility</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Control &amp; Automation</t>
+          <t>Electric Mobility</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Renewable Energy Science and Technology</t>
+          <t>Structural Engineering</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Renewable Energy Science and Technology</t>
+          <t>Structural Engineering</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1987,12 +1987,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Engineering Analysis &amp; Design</t>
+          <t>Polymer Science and Technology</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Engineering Analysis &amp; Design</t>
+          <t>Polymer Science and Technology</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Radio Frequency Design and Technology</t>
+          <t>Optoelectronics And Optical Communication</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Radio Frequency Design and Technology</t>
+          <t>Optoelectronics And Optical Communication</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Biomolecular and Bioprocess Engineering</t>
+          <t>Water Resources Engineering</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Biomolecular and Bioprocess Engineering</t>
+          <t>Water Resources Engineering</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rock Engineering And Underground Structures</t>
+          <t>Control &amp; Automation</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rock Engineering And Underground Structures</t>
+          <t>Control &amp; Automation</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2235,12 +2235,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Solid State Materials</t>
+          <t>Renewable Energy Science and Technology</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Solid State Materials</t>
+          <t>Renewable Energy Science and Technology</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Engineering Analysis &amp; Design</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Engineering Analysis &amp; Design</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Applied Optics</t>
+          <t>Radio Frequency Design and Technology</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Applied Optics</t>
+          <t>Radio Frequency Design and Technology</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thermal Engineering</t>
+          <t>Biomolecular and Bioprocess Engineering</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thermal Engineering</t>
+          <t>Biomolecular and Bioprocess Engineering</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Production Engineering</t>
+          <t>Rock Engineering And Underground Structures</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Production Engineering</t>
+          <t>Rock Engineering And Underground Structures</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atmospheric-Oceanic Science and Technology</t>
+          <t>Solid State Materials</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Atmospheric-Oceanic Science and Technology</t>
+          <t>Solid State Materials</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Power System Engineering</t>
+          <t>Transportation Engineering</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Power System Engineering</t>
+          <t>Transportation Engineering</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Energy Studies</t>
+          <t>Applied Optics</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Energy Studies</t>
+          <t>Applied Optics</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Electronics Circuit &amp; System</t>
+          <t>Thermal Engineering</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Electronics Circuit &amp; System</t>
+          <t>Thermal Engineering</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Telecommunication Engineering</t>
+          <t>Production Engineering</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Telecommunication Engineering</t>
+          <t>Production Engineering</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Atmospheric-Oceanic Science and Technology</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Atmospheric-Oceanic Science and Technology</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fibre Science and Technology</t>
+          <t>Power System Engineering</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fibre Science and Technology</t>
+          <t>Power System Engineering</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Construction Technology</t>
+          <t>Energy Studies</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Construction Technology</t>
+          <t>Energy Studies</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Industrial Engineering</t>
+          <t>Electronics Circuit &amp; System</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Industrial Engineering</t>
+          <t>Electronics Circuit &amp; System</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Communication Systems</t>
+          <t>Telecommunication Engineering</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Communication Systems</t>
+          <t>Telecommunication Engineering</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Computing and Intelligent Systems Engineering</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Computing and Intelligent Systems Engineering</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Energy Science and Engineering</t>
+          <t>Fibre Science and Technology</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Energy Science and Engineering</t>
+          <t>Fibre Science and Technology</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Geotechnical And Geoenvirnomental Engineering</t>
+          <t>Construction Technology</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Geotechnical And Geoenvirnomental Engineering</t>
+          <t>Construction Technology</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Molecular Engineering &amp; Advanced Chemical Analysis</t>
+          <t>Industrial Engineering</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Molecular Engineering &amp; Advanced Chemical Analysis</t>
+          <t>Industrial Engineering</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Photonics</t>
+          <t>Communication Systems</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Photonics</t>
+          <t>Communication Systems</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Smart and Sustainable Power Systems</t>
+          <t>Computing and Intelligent Systems Engineering</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Smart and Sustainable Power Systems</t>
+          <t>Computing and Intelligent Systems Engineering</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Systems, Learning &amp; Control</t>
+          <t>Energy Science and Engineering</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Systems, Learning &amp; Control</t>
+          <t>Energy Science and Engineering</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3594,27 +3594,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Geotechnical And Geoenvirnomental Engineering</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Geotechnical And Geoenvirnomental Engineering</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -3656,27 +3656,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mathematics And Computing</t>
+          <t>Molecular Engineering &amp; Advanced Chemical Analysis</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mathematics And Computing</t>
+          <t>Molecular Engineering &amp; Advanced Chemical Analysis</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -3718,27 +3718,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Engineering and Computational Mechanics</t>
+          <t>Photonics</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Engineering and Computational Mechanics</t>
+          <t>Photonics</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -3780,27 +3780,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Electrical Engineering [Power And Automation]</t>
+          <t>Smart and Sustainable Power Systems</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Electrical Engineering [Power And Automation]</t>
+          <t>Smart and Sustainable Power Systems</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -3842,27 +3842,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Biotechnology And Biochemical Engineering</t>
+          <t>Systems, Learning &amp; Control</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Biotechnology And Biochemical Engineering</t>
+          <t>Systems, Learning &amp; Control</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Mathematics And Computing</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Mathematics And Computing</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Engineering Physics</t>
+          <t>Engineering and Computational Mechanics</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Engineering Physics</t>
+          <t>Engineering and Computational Mechanics</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Industrial &amp; Production Engineering</t>
+          <t>Electrical Engineering [Power And Automation]</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Industrial &amp; Production Engineering</t>
+          <t>Electrical Engineering [Power And Automation]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Biotechnology And Biochemical Engineering</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Biotechnology And Biochemical Engineering</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Design Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Design Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Energy Engineering</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Energy Engineering</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Material Science Engineering</t>
+          <t>Industrial &amp; Production Engineering</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Material Science Engineering</t>
+          <t>Industrial &amp; Production Engineering</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Power and Automation</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Power and Automation</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4524,27 +4524,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Machine Intelligence &amp; Data Science</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Machine Intelligence &amp; Data Science</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -4586,27 +4586,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Biochemical Engineering and Biotechnology</t>
+          <t>Design Engineering</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Biochemical Engineering and Biotechnology</t>
+          <t>Design Engineering</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -4648,27 +4648,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Energy Engineering</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Energy Engineering</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -4710,27 +4710,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Biological Science</t>
+          <t>Material Science Engineering</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Biological Science</t>
+          <t>Material Science Engineering</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -4772,27 +4772,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Power and Automation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Power and Automation</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Machine Intelligence &amp; Data Science</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Machine Intelligence &amp; Data Science</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Biochemical Engineering and Biotechnology</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Biochemical Engineering and Biotechnology</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Telecommunication Technology And Management</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Telecommunication Technology And Management</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sensors, Instrumentation and Cyber-Physical Systems Engineering</t>
+          <t>Biological Science</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sensors, Instrumentation and Cyber-Physical Systems Engineering</t>
+          <t>Biological Science</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Transportation Safety and Injury Prevention</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Transportation Safety and Injury Prevention</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Automotive Research and Tribology</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Automotive Research and Tribology</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5273,12 +5273,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Telecommunication Technology And Management</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Telecommunication Technology And Management</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Sensors, Instrumentation and Cyber-Physical Systems Engineering</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Sensors, Instrumentation and Cyber-Physical Systems Engineering</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Materials Science and Engineering</t>
+          <t>Transportation Safety and Injury Prevention</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Materials Science and Engineering</t>
+          <t>Transportation Safety and Injury Prevention</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Photonics Science and Engineering</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Photonics Science and Engineering</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>VLSI Design Tools &amp; Technology</t>
+          <t>Automotive Research and Tribology</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VLSI Design Tools &amp; Technology</t>
+          <t>Automotive Research and Tribology</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5578,27 +5578,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ph.D (General)</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.58 Lakhs - 5.07 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5640,27 +5640,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5702,27 +5702,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials Science and Engineering</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials Science and Engineering</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5764,27 +5764,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Humanities And Social Science</t>
+          <t>Photonics Science and Engineering</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Humanities And Social Science</t>
+          <t>Photonics Science and Engineering</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5826,27 +5826,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>VLSI Design Tools &amp; Technology</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>VLSI Design Tools &amp; Technology</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5888,12 +5888,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MPP</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MPP (General)</t>
+          <t>Ph.D (General)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2.36 Lakhs - 5.06 Lakhs</t>
+          <t>1.58 Lakhs - 5.07 Lakhs</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -5950,27 +5950,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MBA (General)</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>12.4 Lakhs - 14.06 Lakhs</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Postgraduation in relevant field</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6012,27 +6012,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>12.4 Lakhs - 14.06 Lakhs</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Postgraduation in relevant field</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6074,27 +6074,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>Humanities And Social Science</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>Humanities And Social Science</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>12.4 Lakhs - 14.06 Lakhs</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Postgraduation in relevant field</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6136,27 +6136,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B.Des</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B.Des (General)</t>
+          <t>Public Policy</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Public Policy</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Postgraduation in relevant field</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>UCEED</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>MPP</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>M.Des (General)</t>
+          <t>MPP (General)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2.76 Lakhs</t>
+          <t>2.36 Lakhs - 5.06 Lakhs</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>CEED</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Executive Programme</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Executive Programme (General)</t>
+          <t>MBA (General)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6275,17 +6275,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.2 Lakhs - 1.79 Lakhs</t>
+          <t>12.4 Lakhs - 14.06 Lakhs</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6322,12 +6322,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EMBA</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>EMBA (General)</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16.32 Lakhs - 18 Lakhs</t>
+          <t>12.4 Lakhs - 14.06 Lakhs</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 60%+</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6384,42 +6384,42 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Executive Programme (CEP)</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Executive Management Program in Strategic Management</t>
+          <t>Telecommunication Systems Management</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Executive Management Program in Strategic Management</t>
+          <t>Telecommunication Systems Management</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>12.4 Lakhs - 14.06 Lakhs</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 60%+</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6446,32 +6446,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Executive Programme (CEP)</t>
+          <t>B.Des</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Executive Management Program in Human Resource Strategic Management</t>
+          <t>B.Des (General)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Executive Management Program in Human Resource Strategic Management</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>UCEED</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6508,55 +6508,365 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>M.Des</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>M.Des (General)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2.76 Lakhs</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>CEED</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Executive Programme</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Executive Programme (General)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.2 Lakhs - 1.79 Lakhs</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>EMBA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>EMBA (General)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>16.32 Lakhs - 18 Lakhs</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>Executive Programme (CEP)</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Executive Management Program in Strategic Management</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Executive Management Program in Strategic Management</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Executive Programme (CEP)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Executive Management Program in Human Resource Strategic Management</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Executive Management Program in Human Resource Strategic Management</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Executive Programme (CEP)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
         <is>
           <t>Executive Program in Robotics</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>Executive Program in Robotics</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>Part Time</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t>PG</t>
         </is>
@@ -6667,7 +6977,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="101" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6710,27 +7020,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2 Cr</t>
+          <t>2,00,00,000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25.82 Lakh</t>
+          <t>25,82,000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20 LPA</t>
+          <t>22.51 Lakh</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>100% Placement</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Microsoft, Google, Amazon, Accenture, TCS, Infosys, Cognizant, HCL, Cisco, Goldman Sachs, Flipkart</t>
+          <t>Not Specified</t>
         </is>
       </c>
     </row>

--- a/exports/colleges/25455_iit-delhi-indian-institute-of-technology-iitd-new-delhi.xlsx
+++ b/exports/colleges/25455_iit-delhi-indian-institute-of-technology-iitd-new-delhi.xlsx
@@ -25,13 +25,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,12 +53,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,72 +453,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>college_type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ownership</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>established_year</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>accreditation</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>affiliation</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ranking</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>overview_description</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>contact_info</t>
         </is>
@@ -593,15 +605,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="35" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
@@ -611,62 +623,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>degree_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>course_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>specialization</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_fees</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>course_type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>eligibility</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>entrance_exam</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>application_date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>intake_seats</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>course_level</t>
         </is>
@@ -995,17 +1007,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>5.06 Lakhs - 5.07 Lakhs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1052,27 +1064,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vlsi Design</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Vlsi Design</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>11.74 Lakhs - 12.93 Lakhs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1087,7 +1099,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1102,7 +1114,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1114,22 +1126,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>2.36 Lakhs - 5.07 Lakhs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1149,7 +1161,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1176,27 +1188,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Computer Technology</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Computer Technology</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>1.58 Lakhs - 5.07 Lakhs</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1211,7 +1223,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1226,7 +1238,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1238,27 +1250,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MPP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Construction Engineering And Management</t>
+          <t>MPP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Construction Engineering And Management</t>
+          <t>MPP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>2.36 Lakhs - 5.06 Lakhs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1273,7 +1285,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1288,7 +1300,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1312,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Biomedical Engineering</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Biomedical Engineering</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>12.4 Lakhs - 14.06 Lakhs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1335,7 +1347,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1362,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Des</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Environmental Engineering</t>
+          <t>B.Des</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Environmental Engineering</t>
+          <t>B.Des</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1397,7 +1409,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>UCEED</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1412,7 +1424,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1424,22 +1436,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mechanical Design</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mechanical Design</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>2.76 Lakhs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1459,7 +1471,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CEED</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1486,32 +1498,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Textile Technology</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Textile Technology</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>1.2 Lakhs - 1.79 Lakhs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1521,7 +1533,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1548,22 +1560,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Power Electronics &amp; Machine Drives</t>
+          <t>EMBA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Power Electronics &amp; Machine Drives</t>
+          <t>EMBA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>16.32 Lakhs - 18 Lakhs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1573,7 +1585,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1583,7 +1595,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1615,12 +1627,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Integrated Circuit Technology</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Integrated Circuit Technology</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1677,12 +1689,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Instrumentation</t>
+          <t>Vlsi Design</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Instrumentation</t>
+          <t>Vlsi Design</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1739,12 +1751,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Material Science And Engineering</t>
+          <t>Cyber Security</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Material Science And Engineering</t>
+          <t>Cyber Security</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1801,12 +1813,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Computer Technology</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Computer Technology</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1863,12 +1875,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Electric Mobility</t>
+          <t>Construction Engineering And Management</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Electric Mobility</t>
+          <t>Construction Engineering And Management</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1925,12 +1937,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Structural Engineering</t>
+          <t>Biomedical Engineering</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Structural Engineering</t>
+          <t>Biomedical Engineering</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1987,12 +1999,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Polymer Science and Technology</t>
+          <t>Environmental Engineering</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Polymer Science and Technology</t>
+          <t>Environmental Engineering</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2049,12 +2061,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Optoelectronics And Optical Communication</t>
+          <t>Mechanical Design</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Optoelectronics And Optical Communication</t>
+          <t>Mechanical Design</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2111,12 +2123,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Water Resources Engineering</t>
+          <t>Textile Technology</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Water Resources Engineering</t>
+          <t>Textile Technology</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2173,12 +2185,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Control &amp; Automation</t>
+          <t>Power Electronics &amp; Machine Drives</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Control &amp; Automation</t>
+          <t>Power Electronics &amp; Machine Drives</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2235,12 +2247,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Renewable Energy Science and Technology</t>
+          <t>Integrated Circuit Technology</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Renewable Energy Science and Technology</t>
+          <t>Integrated Circuit Technology</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2297,12 +2309,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Engineering Analysis &amp; Design</t>
+          <t>Instrumentation</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Engineering Analysis &amp; Design</t>
+          <t>Instrumentation</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2359,12 +2371,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Radio Frequency Design and Technology</t>
+          <t>Material Science And Engineering</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Radio Frequency Design and Technology</t>
+          <t>Material Science And Engineering</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2421,12 +2433,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Biomolecular and Bioprocess Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Biomolecular and Bioprocess Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2483,12 +2495,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rock Engineering And Underground Structures</t>
+          <t>Electric Mobility</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rock Engineering And Underground Structures</t>
+          <t>Electric Mobility</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2545,12 +2557,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Solid State Materials</t>
+          <t>Structural Engineering</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Solid State Materials</t>
+          <t>Structural Engineering</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2607,12 +2619,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Polymer Science and Technology</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Polymer Science and Technology</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2669,12 +2681,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Applied Optics</t>
+          <t>Optoelectronics And Optical Communication</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Applied Optics</t>
+          <t>Optoelectronics And Optical Communication</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2731,12 +2743,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thermal Engineering</t>
+          <t>Water Resources Engineering</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thermal Engineering</t>
+          <t>Water Resources Engineering</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2793,12 +2805,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Production Engineering</t>
+          <t>Control &amp; Automation</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Production Engineering</t>
+          <t>Control &amp; Automation</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2855,12 +2867,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atmospheric-Oceanic Science and Technology</t>
+          <t>Renewable Energy Science and Technology</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Atmospheric-Oceanic Science and Technology</t>
+          <t>Renewable Energy Science and Technology</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2917,12 +2929,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Power System Engineering</t>
+          <t>Engineering Analysis &amp; Design</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Power System Engineering</t>
+          <t>Engineering Analysis &amp; Design</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2979,12 +2991,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Energy Studies</t>
+          <t>Radio Frequency Design and Technology</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Energy Studies</t>
+          <t>Radio Frequency Design and Technology</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3041,12 +3053,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Electronics Circuit &amp; System</t>
+          <t>Biomolecular and Bioprocess Engineering</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Electronics Circuit &amp; System</t>
+          <t>Biomolecular and Bioprocess Engineering</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3103,12 +3115,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Telecommunication Engineering</t>
+          <t>Rock Engineering And Underground Structures</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Telecommunication Engineering</t>
+          <t>Rock Engineering And Underground Structures</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3165,12 +3177,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Solid State Materials</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Solid State Materials</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3227,12 +3239,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fibre Science and Technology</t>
+          <t>Transportation Engineering</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fibre Science and Technology</t>
+          <t>Transportation Engineering</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3289,12 +3301,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Construction Technology</t>
+          <t>Applied Optics</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Construction Technology</t>
+          <t>Applied Optics</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3351,12 +3363,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Industrial Engineering</t>
+          <t>Thermal Engineering</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Industrial Engineering</t>
+          <t>Thermal Engineering</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3413,12 +3425,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Communication Systems</t>
+          <t>Production Engineering</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Communication Systems</t>
+          <t>Production Engineering</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3475,12 +3487,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Computing and Intelligent Systems Engineering</t>
+          <t>Atmospheric-Oceanic Science and Technology</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Computing and Intelligent Systems Engineering</t>
+          <t>Atmospheric-Oceanic Science and Technology</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3537,12 +3549,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Energy Science and Engineering</t>
+          <t>Power System Engineering</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Energy Science and Engineering</t>
+          <t>Power System Engineering</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3599,12 +3611,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Geotechnical And Geoenvirnomental Engineering</t>
+          <t>Energy Studies</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Geotechnical And Geoenvirnomental Engineering</t>
+          <t>Energy Studies</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3661,12 +3673,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Molecular Engineering &amp; Advanced Chemical Analysis</t>
+          <t>Electronics Circuit &amp; System</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Molecular Engineering &amp; Advanced Chemical Analysis</t>
+          <t>Electronics Circuit &amp; System</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3723,12 +3735,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Photonics</t>
+          <t>Telecommunication Engineering</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Photonics</t>
+          <t>Telecommunication Engineering</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3785,12 +3797,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Smart and Sustainable Power Systems</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Smart and Sustainable Power Systems</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3847,12 +3859,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Systems, Learning &amp; Control</t>
+          <t>Fibre Science and Technology</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Systems, Learning &amp; Control</t>
+          <t>Fibre Science and Technology</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3904,27 +3916,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Construction Technology</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Construction Technology</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3939,7 +3951,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3954,7 +3966,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -3966,27 +3978,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mathematics And Computing</t>
+          <t>Industrial Engineering</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mathematics And Computing</t>
+          <t>Industrial Engineering</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4001,7 +4013,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4016,7 +4028,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4028,27 +4040,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Engineering and Computational Mechanics</t>
+          <t>Communication Systems</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Engineering and Computational Mechanics</t>
+          <t>Communication Systems</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4063,7 +4075,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4078,7 +4090,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4090,27 +4102,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Electrical Engineering [Power And Automation]</t>
+          <t>Computing and Intelligent Systems Engineering</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Electrical Engineering [Power And Automation]</t>
+          <t>Computing and Intelligent Systems Engineering</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4125,7 +4137,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4140,7 +4152,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4152,27 +4164,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Biotechnology And Biochemical Engineering</t>
+          <t>Energy Science and Engineering</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Biotechnology And Biochemical Engineering</t>
+          <t>Energy Science and Engineering</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4187,7 +4199,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4202,7 +4214,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4214,27 +4226,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Geotechnical And Geoenvirnomental Engineering</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Geotechnical And Geoenvirnomental Engineering</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4249,7 +4261,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4264,7 +4276,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4276,27 +4288,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Molecular Engineering &amp; Advanced Chemical Analysis</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Molecular Engineering &amp; Advanced Chemical Analysis</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4311,7 +4323,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4326,7 +4338,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4338,27 +4350,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Engineering Physics</t>
+          <t>Photonics</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Engineering Physics</t>
+          <t>Photonics</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4373,7 +4385,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4388,7 +4400,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4400,27 +4412,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Industrial &amp; Production Engineering</t>
+          <t>Smart and Sustainable Power Systems</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Industrial &amp; Production Engineering</t>
+          <t>Smart and Sustainable Power Systems</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4435,7 +4447,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4450,7 +4462,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4462,27 +4474,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Systems, Learning &amp; Control</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Systems, Learning &amp; Control</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4497,7 +4509,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4512,7 +4524,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4529,12 +4541,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4591,12 +4603,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Design Engineering</t>
+          <t>Mathematics And Computing</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Design Engineering</t>
+          <t>Mathematics And Computing</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4653,12 +4665,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Energy Engineering</t>
+          <t>Engineering and Computational Mechanics</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Energy Engineering</t>
+          <t>Engineering and Computational Mechanics</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4715,12 +4727,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Material Science Engineering</t>
+          <t>Electrical Engineering [Power And Automation]</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Material Science Engineering</t>
+          <t>Electrical Engineering [Power And Automation]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4777,12 +4789,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Power and Automation</t>
+          <t>Biotechnology And Biochemical Engineering</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Power and Automation</t>
+          <t>Biotechnology And Biochemical Engineering</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4834,27 +4846,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Machine Intelligence &amp; Data Science</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Machine Intelligence &amp; Data Science</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4869,7 +4881,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4884,7 +4896,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -4896,27 +4908,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Biochemical Engineering and Biotechnology</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Biochemical Engineering and Biotechnology</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4931,7 +4943,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4946,7 +4958,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -4958,27 +4970,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4993,7 +5005,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5008,7 +5020,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5020,27 +5032,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Biological Science</t>
+          <t>Industrial &amp; Production Engineering</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Biological Science</t>
+          <t>Industrial &amp; Production Engineering</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5055,7 +5067,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5070,7 +5082,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5082,27 +5094,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5117,7 +5129,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5132,7 +5144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5144,27 +5156,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5179,7 +5191,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5194,7 +5206,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5206,27 +5218,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Design Engineering</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Design Engineering</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5241,7 +5253,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5256,7 +5268,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5268,27 +5280,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Telecommunication Technology And Management</t>
+          <t>Energy Engineering</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Telecommunication Technology And Management</t>
+          <t>Energy Engineering</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5303,7 +5315,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5318,7 +5330,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5330,27 +5342,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sensors, Instrumentation and Cyber-Physical Systems Engineering</t>
+          <t>Material Science Engineering</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sensors, Instrumentation and Cyber-Physical Systems Engineering</t>
+          <t>Material Science Engineering</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5365,7 +5377,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5380,7 +5392,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5392,27 +5404,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Transportation Safety and Injury Prevention</t>
+          <t>Power and Automation</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Transportation Safety and Injury Prevention</t>
+          <t>Power and Automation</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5427,7 +5439,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5442,7 +5454,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5459,12 +5471,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Machine Intelligence &amp; Data Science</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Machine Intelligence &amp; Data Science</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5521,12 +5533,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Automotive Research and Tribology</t>
+          <t>Biochemical Engineering and Biotechnology</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Automotive Research and Tribology</t>
+          <t>Biochemical Engineering and Biotechnology</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5583,12 +5595,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5645,12 +5657,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biological Science</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Biological Science</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5707,12 +5719,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Materials Science and Engineering</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Materials Science and Engineering</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5769,12 +5781,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Photonics Science and Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Photonics Science and Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5831,12 +5843,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VLSI Design Tools &amp; Technology</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VLSI Design Tools &amp; Technology</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5888,27 +5900,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ph.D (General)</t>
+          <t>Telecommunication Technology And Management</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Telecommunication Technology And Management</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.58 Lakhs - 5.07 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5923,7 +5935,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5938,7 +5950,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5950,27 +5962,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Sensors, Instrumentation and Cyber-Physical Systems Engineering</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Sensors, Instrumentation and Cyber-Physical Systems Engineering</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5980,12 +5992,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6000,7 +6012,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6012,27 +6024,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Transportation Safety and Injury Prevention</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Transportation Safety and Injury Prevention</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6042,12 +6054,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6062,7 +6074,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6074,27 +6086,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Humanities And Social Science</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Humanities And Social Science</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6104,12 +6116,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6124,7 +6136,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6136,27 +6148,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Automotive Research and Tribology</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Automotive Research and Tribology</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6166,12 +6178,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6186,7 +6198,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6198,22 +6210,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MPP</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MPP (General)</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2.36 Lakhs - 5.06 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6233,7 +6245,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6260,22 +6272,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MBA (General)</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>12.4 Lakhs - 14.06 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6295,7 +6307,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6322,22 +6334,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Materials Science and Engineering</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Materials Science and Engineering</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>12.4 Lakhs - 14.06 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6352,12 +6364,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6384,22 +6396,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>Photonics Science and Engineering</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>Photonics Science and Engineering</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>12.4 Lakhs - 14.06 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6414,12 +6426,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6446,27 +6458,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B.Des</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B.Des (General)</t>
+          <t>VLSI Design Tools &amp; Technology</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>VLSI Design Tools &amp; Technology</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6481,7 +6493,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>UCEED</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6496,7 +6508,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6508,12 +6520,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>M.Des (General)</t>
+          <t>Ph.D (General)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6523,12 +6535,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2.76 Lakhs</t>
+          <t>1.58 Lakhs - 5.07 Lakhs</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6543,7 +6555,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>CEED</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6558,7 +6570,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6570,42 +6582,42 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Executive Programme</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Executive Programme (General)</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.2 Lakhs - 1.79 Lakhs</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Postgraduation in relevant field</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6620,7 +6632,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6632,42 +6644,42 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EMBA</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>EMBA (General)</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>16.32 Lakhs - 18 Lakhs</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Postgraduation in relevant field</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6682,7 +6694,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6694,42 +6706,42 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Executive Programme (CEP)</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Executive Management Program in Strategic Management</t>
+          <t>Humanities And Social Science</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Executive Management Program in Strategic Management</t>
+          <t>Humanities And Social Science</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Postgraduation in relevant field</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6744,7 +6756,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6756,42 +6768,42 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Executive Programme (CEP)</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Executive Management Program in Human Resource Strategic Management</t>
+          <t>Public Policy</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Executive Management Program in Human Resource Strategic Management</t>
+          <t>Public Policy</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Postgraduation in relevant field</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6806,7 +6818,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -6818,55 +6830,675 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>MPP (General)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2.36 Lakhs - 5.06 Lakhs</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MBA (General)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>12.4 Lakhs - 14.06 Lakhs</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>12.4 Lakhs - 14.06 Lakhs</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Graduation with 60%+</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Telecommunication Systems Management</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Telecommunication Systems Management</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>12.4 Lakhs - 14.06 Lakhs</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Graduation with 60%+</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>B.Des</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>B.Des (General)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>11.74 Lakhs</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>4 Years</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>UCEED</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>M.Des</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>M.Des (General)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2.76 Lakhs</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>CEED</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Executive Programme</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Executive Programme (General)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1.2 Lakhs - 1.79 Lakhs</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>EMBA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EMBA (General)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>16.32 Lakhs - 18 Lakhs</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
           <t>Executive Programme (CEP)</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Executive Management Program in Strategic Management</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Executive Management Program in Strategic Management</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Executive Programme (CEP)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Executive Management Program in Human Resource Strategic Management</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Executive Management Program in Human Resource Strategic Management</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Executive Programme (CEP)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
         <is>
           <t>Executive Program in Robotics</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>Executive Program in Robotics</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>Part Time</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t>PG</t>
         </is>
@@ -6895,32 +7527,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>admission_process</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>exams_accepted</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>eligibility_criteria</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>important_dates</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>application_deadlines</t>
         </is>
@@ -6981,32 +7613,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>highest_package</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>average_package</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>median_package</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>placement_percentage</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>top_recruiters</t>
         </is>
@@ -7065,22 +7697,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ranking_body</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ranking_year</t>
         </is>
@@ -7123,12 +7755,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -7157,22 +7789,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="93" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>status</t>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>scholarship_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>eligibility</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>amount</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7828,193 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>No Data Available</t>
+          <t>Name of the Scholarship</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1984 Batch Scholarship</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1st-year student of UG Programme</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ABB Scholarship</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2nd-year student in Electrical Engineering/ Power with 7.5 CGPA or above</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Amar Chand Memorial Scholarship</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1st-year student of M.Sc (Mathematics) securing a high CGPA at the end of the 1st semester</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Indian Women's Association Bonn Scholarship</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1st year UG Student</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jain Scholarship</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1st year UG Student based on JEE Rank &amp; a minimum CGPA of 7.5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Janak Raj Malhotra Scholarship</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1st year UG Student</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Krishna Engineering Scholarship</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1st year UG Student</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Prof. A.K. Mahalanabis Memorial Scholarship</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1st year UG Student of Electrical Engineering with highest JEE Rank</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
         </is>
       </c>
     </row>
@@ -7208,17 +8038,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>hostel_fees</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>facilities</t>
         </is>
@@ -7252,32 +8082,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="496" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>college_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>reviewer_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>review_text</t>
         </is>
@@ -7291,7 +8121,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aditya Sharma</t>
+          <t>Alumni Reviewer</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -7299,7 +8129,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Excellent academic atmosphere, world class research facilities, and amazing placements.</t>
+          <t>Pros: My friend got a scholarship so i can verify it truly happens and is a great opportunity for students with low parental income to ease their parent's financial pressure The college has really good placements, a lot of companies offer a lot of job opportunities and the packages are quite high as well. Faculty expertise: iit delhi often attracts experienced and knowledgeable faculty members who are experts in their respective fields. students benefit from their guidance and mentorship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Student Reviewer</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Cons: The hostel facilities are not as good as expected the meal is too bad. The race academy curriculum at iit delhi can be intense and demanding a leading to high levels of stress and pressure among students</t>
         </is>
       </c>
     </row>

--- a/exports/colleges/25455_iit-delhi-indian-institute-of-technology-iitd-new-delhi.xlsx
+++ b/exports/colleges/25455_iit-delhi-indian-institute-of-technology-iitd-new-delhi.xlsx
@@ -7747,11 +7747,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="83" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7762,7 +7764,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>designation</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>department</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7786,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>No Data Available</t>
+          <t>Professors are legit best . They have more than enough knowledge of their field.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
         </is>
       </c>
     </row>

--- a/exports/colleges/25455_iit-delhi-indian-institute-of-technology-iitd-new-delhi.xlsx
+++ b/exports/colleges/25455_iit-delhi-indian-institute-of-technology-iitd-new-delhi.xlsx
@@ -445,7 +445,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="253" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="165" customWidth="1" min="13" max="13"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CD Rank #1</t>
+          <t>Rank #1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,19 +605,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="93" customWidth="1" min="3" max="3"/>
+    <col width="93" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="35" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -707,12 +707,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>5.06 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Graduation with 60% + GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GATE, COAP</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>22 Mar - 07 Apr 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>11.74 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10+2 with 75% + JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JEE Main, JEE Advanced</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.36 Lakhs</t>
+          <t>2.36 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Graduation with 55% + IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IIT JAM, JOAPS</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 15 Apr 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>M.Phil/Ph.D in Engineering</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>3.4 L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Post Graduation with 60%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>22 Mar - 07 Apr 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Master of Science [M.S]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Master of Science [M.S]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>5.07 L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Graduation with 60% + GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GATE, IIT JAM, COAP, JOAPS</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 15 Apr 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MPP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Master of Public Policy [MPP]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Master of Public Policy [MPP]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5.06 Lakhs - 5.07 Lakhs</t>
+          <t>5.06 L</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>22 Mar - 07 Apr 2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.74 Lakhs - 12.93 Lakhs</t>
+          <t>14.06 L</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Aug - 13 Sept 2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Des</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Bachelor of Design [B.Des]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Bachelor of Design [B.Des]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.36 Lakhs - 5.07 Lakhs</t>
+          <t>11.74 L</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>UCEED</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>14 Mar - 03 Apr 2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1193,27 +1193,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>Ph.D.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>Ph.D.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.58 Lakhs - 5.07 Lakhs</t>
+          <t>1.58 L</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>22 Mar - 07 Apr 2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1250,27 +1250,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MPP</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MPP</t>
+          <t>Bachelor of Technology [B.Tech] + Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MPP</t>
+          <t>Bachelor of Technology [B.Tech] + Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.36 Lakhs - 5.06 Lakhs</t>
+          <t>12.93 L</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Master of Design [M.Des] (Industrial Design)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Master of Design [M.Des] (Industrial Design)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12.4 Lakhs - 14.06 Lakhs</t>
+          <t>2.76 L</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>CEED</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>22 Mar - 07 Apr 2026</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1374,32 +1374,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B.Des</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B.Des</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B.Des</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>1.2 L - 1.79 L</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>UCEED</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 June 2026</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1436,32 +1436,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>Master of Business Administration [MBA] (Technology Management)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>Master of Business Administration [MBA] (Technology Management)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2.76 Lakhs</t>
+          <t>12.4 L</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CEED</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Aug - 13 Sept 2026</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1498,32 +1498,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Executive Programme</t>
+          <t>Post Graduate Diploma in Naval Construction</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Executive Programme</t>
+          <t>Post Graduate Diploma in Naval Construction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Executive Programme</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.2 Lakhs - 1.79 Lakhs</t>
+          <t>5.06 L</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1560,32 +1560,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Bachelor of Science [BS] (Chemistry)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EMBA</t>
+          <t>Bachelor of Science [BS] (Chemistry)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EMBA</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16.32 Lakhs - 18 Lakhs</t>
+          <t>11.74 L</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 June - 14 Jul 2021</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1622,27 +1622,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>Master of Arts [MA] (Society and Culture)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>Master of Arts [MA] (Society and Culture)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>2.36 L</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>22 Mar - 07 Apr 2026</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1684,32 +1684,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vlsi Design</t>
+          <t>Post Graduate Program for Executives for Visionary Leadership In Manufacturing [PGPEX-VLM]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Vlsi Design</t>
+          <t>Post Graduate Program for Executives for Visionary Leadership In Manufacturing [PGPEX-VLM]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>16.32 L</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 Jan - 15 Apr 2026</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 60% + GATE</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>GATE, COAP</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1808,27 +1808,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Computer Technology</t>
+          <t>Bachelor of Technology [B.Tech]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Computer Technology</t>
+          <t>Bachelor of Technology [B.Tech]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 75% + JEE Advanced</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Main, JEE Advanced</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1870,22 +1870,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Construction Engineering And Management</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Construction Engineering And Management</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>2.36 Lakhs</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 55% + IIT JAM</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>IIT JAM, JOAPS</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1932,27 +1932,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Biomedical Engineering</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Biomedical Engineering</t>
+          <t>M.Phil/Ph.D in Engineering</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Post Graduation with 60%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1994,22 +1994,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Environmental Engineering</t>
+          <t>Master of Science [M.S]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Environmental Engineering</t>
+          <t>Master of Science [M.S]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 60% + GATE</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>GATE, IIT JAM, COAP, JOAPS</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mechanical Design</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mechanical Design</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>5.06 Lakhs - 5.07 Lakhs</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2118,27 +2118,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Textile Technology</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Textile Technology</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>11.74 Lakhs - 12.93 Lakhs</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2180,22 +2180,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Power Electronics &amp; Machine Drives</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Power Electronics &amp; Machine Drives</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>2.36 Lakhs - 5.07 Lakhs</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2242,27 +2242,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Integrated Circuit Technology</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Integrated Circuit Technology</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>1.58 Lakhs - 5.07 Lakhs</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -2304,27 +2304,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MPP</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Instrumentation</t>
+          <t>MPP</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Instrumentation</t>
+          <t>MPP</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>2.36 Lakhs - 5.06 Lakhs</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2366,22 +2366,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Material Science And Engineering</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Material Science And Engineering</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>12.4 Lakhs - 14.06 Lakhs</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2428,27 +2428,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Des</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>B.Des</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>B.Des</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>UCEED</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2490,22 +2490,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Electric Mobility</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Electric Mobility</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>2.76 Lakhs</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CEED</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2552,32 +2552,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Structural Engineering</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Structural Engineering</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>1.2 Lakhs - 1.79 Lakhs</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2614,22 +2614,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Polymer Science and Technology</t>
+          <t>EMBA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Polymer Science and Technology</t>
+          <t>EMBA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5.06 Lakhs</t>
+          <t>16.32 Lakhs - 18 Lakhs</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Optoelectronics And Optical Communication</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Optoelectronics And Optical Communication</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2743,12 +2743,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Water Resources Engineering</t>
+          <t>Vlsi Design</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Water Resources Engineering</t>
+          <t>Vlsi Design</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Control &amp; Automation</t>
+          <t>Cyber Security</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Control &amp; Automation</t>
+          <t>Cyber Security</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Renewable Energy Science and Technology</t>
+          <t>Computer Technology</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Renewable Energy Science and Technology</t>
+          <t>Computer Technology</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Engineering Analysis &amp; Design</t>
+          <t>Construction Engineering And Management</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Engineering Analysis &amp; Design</t>
+          <t>Construction Engineering And Management</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Radio Frequency Design and Technology</t>
+          <t>Biomedical Engineering</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Radio Frequency Design and Technology</t>
+          <t>Biomedical Engineering</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Biomolecular and Bioprocess Engineering</t>
+          <t>Environmental Engineering</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Biomolecular and Bioprocess Engineering</t>
+          <t>Environmental Engineering</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rock Engineering And Underground Structures</t>
+          <t>Mechanical Design</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Rock Engineering And Underground Structures</t>
+          <t>Mechanical Design</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Solid State Materials</t>
+          <t>Textile Technology</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Solid State Materials</t>
+          <t>Textile Technology</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Power Electronics &amp; Machine Drives</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Power Electronics &amp; Machine Drives</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Applied Optics</t>
+          <t>Integrated Circuit Technology</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Applied Optics</t>
+          <t>Integrated Circuit Technology</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thermal Engineering</t>
+          <t>Instrumentation</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Thermal Engineering</t>
+          <t>Instrumentation</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Production Engineering</t>
+          <t>Material Science And Engineering</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Production Engineering</t>
+          <t>Material Science And Engineering</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atmospheric-Oceanic Science and Technology</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Atmospheric-Oceanic Science and Technology</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Power System Engineering</t>
+          <t>Electric Mobility</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Power System Engineering</t>
+          <t>Electric Mobility</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Energy Studies</t>
+          <t>Structural Engineering</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Energy Studies</t>
+          <t>Structural Engineering</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Electronics Circuit &amp; System</t>
+          <t>Polymer Science and Technology</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Electronics Circuit &amp; System</t>
+          <t>Polymer Science and Technology</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Telecommunication Engineering</t>
+          <t>Optoelectronics And Optical Communication</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Telecommunication Engineering</t>
+          <t>Optoelectronics And Optical Communication</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Water Resources Engineering</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Water Resources Engineering</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fibre Science and Technology</t>
+          <t>Control &amp; Automation</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fibre Science and Technology</t>
+          <t>Control &amp; Automation</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Construction Technology</t>
+          <t>Renewable Energy Science and Technology</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Construction Technology</t>
+          <t>Renewable Energy Science and Technology</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Industrial Engineering</t>
+          <t>Engineering Analysis &amp; Design</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Industrial Engineering</t>
+          <t>Engineering Analysis &amp; Design</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Communication Systems</t>
+          <t>Radio Frequency Design and Technology</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Communication Systems</t>
+          <t>Radio Frequency Design and Technology</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Computing and Intelligent Systems Engineering</t>
+          <t>Biomolecular and Bioprocess Engineering</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Computing and Intelligent Systems Engineering</t>
+          <t>Biomolecular and Bioprocess Engineering</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Energy Science and Engineering</t>
+          <t>Rock Engineering And Underground Structures</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Energy Science and Engineering</t>
+          <t>Rock Engineering And Underground Structures</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Geotechnical And Geoenvirnomental Engineering</t>
+          <t>Solid State Materials</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Geotechnical And Geoenvirnomental Engineering</t>
+          <t>Solid State Materials</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Molecular Engineering &amp; Advanced Chemical Analysis</t>
+          <t>Transportation Engineering</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Molecular Engineering &amp; Advanced Chemical Analysis</t>
+          <t>Transportation Engineering</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Photonics</t>
+          <t>Applied Optics</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Photonics</t>
+          <t>Applied Optics</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Smart and Sustainable Power Systems</t>
+          <t>Thermal Engineering</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Smart and Sustainable Power Systems</t>
+          <t>Thermal Engineering</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Systems, Learning &amp; Control</t>
+          <t>Production Engineering</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Systems, Learning &amp; Control</t>
+          <t>Production Engineering</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4536,27 +4536,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Atmospheric-Oceanic Science and Technology</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Atmospheric-Oceanic Science and Technology</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4598,27 +4598,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mathematics And Computing</t>
+          <t>Power System Engineering</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mathematics And Computing</t>
+          <t>Power System Engineering</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4660,27 +4660,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Engineering and Computational Mechanics</t>
+          <t>Energy Studies</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Engineering and Computational Mechanics</t>
+          <t>Energy Studies</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4722,27 +4722,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Electrical Engineering [Power And Automation]</t>
+          <t>Electronics Circuit &amp; System</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Electrical Engineering [Power And Automation]</t>
+          <t>Electronics Circuit &amp; System</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4784,27 +4784,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Biotechnology And Biochemical Engineering</t>
+          <t>Telecommunication Engineering</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Biotechnology And Biochemical Engineering</t>
+          <t>Telecommunication Engineering</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4846,27 +4846,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4908,27 +4908,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Fibre Science and Technology</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Fibre Science and Technology</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4970,27 +4970,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Engineering Physics</t>
+          <t>Construction Technology</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Engineering Physics</t>
+          <t>Construction Technology</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5032,27 +5032,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Industrial &amp; Production Engineering</t>
+          <t>Industrial Engineering</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Industrial &amp; Production Engineering</t>
+          <t>Industrial Engineering</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5094,27 +5094,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Communication Systems</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Communication Systems</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5156,27 +5156,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Computing and Intelligent Systems Engineering</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Computing and Intelligent Systems Engineering</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5218,27 +5218,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Design Engineering</t>
+          <t>Energy Science and Engineering</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Design Engineering</t>
+          <t>Energy Science and Engineering</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5280,27 +5280,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Energy Engineering</t>
+          <t>Geotechnical And Geoenvirnomental Engineering</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Energy Engineering</t>
+          <t>Geotechnical And Geoenvirnomental Engineering</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5342,27 +5342,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Material Science Engineering</t>
+          <t>Molecular Engineering &amp; Advanced Chemical Analysis</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Material Science Engineering</t>
+          <t>Molecular Engineering &amp; Advanced Chemical Analysis</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5404,27 +5404,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Power and Automation</t>
+          <t>Photonics</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Power and Automation</t>
+          <t>Photonics</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5466,22 +5466,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Machine Intelligence &amp; Data Science</t>
+          <t>Smart and Sustainable Power Systems</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Machine Intelligence &amp; Data Science</t>
+          <t>Smart and Sustainable Power Systems</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5528,22 +5528,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Biochemical Engineering and Biotechnology</t>
+          <t>Systems, Learning &amp; Control</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Biochemical Engineering and Biotechnology</t>
+          <t>Systems, Learning &amp; Control</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>5.06 Lakhs</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5652,27 +5652,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Biological Science</t>
+          <t>Mathematics And Computing</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Biological Science</t>
+          <t>Mathematics And Computing</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5714,27 +5714,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Engineering and Computational Mechanics</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Engineering and Computational Mechanics</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5776,27 +5776,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Electrical Engineering [Power And Automation]</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Electrical Engineering [Power And Automation]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5838,27 +5838,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Biotechnology And Biochemical Engineering</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Biotechnology And Biochemical Engineering</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5900,27 +5900,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Telecommunication Technology And Management</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Telecommunication Technology And Management</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5962,27 +5962,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sensors, Instrumentation and Cyber-Physical Systems Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sensors, Instrumentation and Cyber-Physical Systems Engineering</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6024,27 +6024,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Transportation Safety and Injury Prevention</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Transportation Safety and Injury Prevention</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6086,27 +6086,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Industrial &amp; Production Engineering</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Applied Mechanics</t>
+          <t>Industrial &amp; Production Engineering</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6148,27 +6148,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Automotive Research and Tribology</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Automotive Research and Tribology</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6210,27 +6210,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6272,27 +6272,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Design Engineering</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Design Engineering</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6334,27 +6334,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Materials Science and Engineering</t>
+          <t>Energy Engineering</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Materials Science and Engineering</t>
+          <t>Energy Engineering</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6396,27 +6396,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Photonics Science and Engineering</t>
+          <t>Material Science Engineering</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Photonics Science and Engineering</t>
+          <t>Material Science Engineering</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6458,27 +6458,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VLSI Design Tools &amp; Technology</t>
+          <t>Power and Automation</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VLSI Design Tools &amp; Technology</t>
+          <t>Power and Automation</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>5.07 Lakhs</t>
+          <t>11.74 Lakhs</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -6520,27 +6520,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ph.D (General)</t>
+          <t>Machine Intelligence &amp; Data Science</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Machine Intelligence &amp; Data Science</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.58 Lakhs - 5.07 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6582,27 +6582,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Biochemical Engineering and Biotechnology</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Biochemical Engineering and Biotechnology</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6644,27 +6644,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6706,27 +6706,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Humanities And Social Science</t>
+          <t>Biological Science</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Humanities And Social Science</t>
+          <t>Biological Science</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6768,27 +6768,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -6830,22 +6830,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MPP</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MPP (General)</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2.36 Lakhs - 5.06 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6892,22 +6892,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MBA (General)</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>12.4 Lakhs - 14.06 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Telecommunication Technology And Management</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Telecommunication Technology And Management</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>12.4 Lakhs - 14.06 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -7016,22 +7016,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>Sensors, Instrumentation and Cyber-Physical Systems Engineering</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>Sensors, Instrumentation and Cyber-Physical Systems Engineering</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>12.4 Lakhs - 14.06 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7078,27 +7078,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B.Des</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B.Des (General)</t>
+          <t>Transportation Safety and Injury Prevention</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Transportation Safety and Injury Prevention</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>11.74 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>UCEED</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -7140,22 +7140,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>M.Des (General)</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Applied Mechanics</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2.76 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CEED</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7202,32 +7202,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Executive Programme</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Executive Programme (General)</t>
+          <t>Automotive Research and Tribology</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Automotive Research and Tribology</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.2 Lakhs - 1.79 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7264,22 +7264,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EMBA</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>EMBA (General)</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>16.32 Lakhs - 18 Lakhs</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7326,32 +7326,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Executive Programme (CEP)</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Executive Management Program in Strategic Management</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Executive Management Program in Strategic Management</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7388,32 +7388,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Executive Programme (CEP)</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Executive Management Program in Human Resource Strategic Management</t>
+          <t>Materials Science and Engineering</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Executive Management Program in Human Resource Strategic Management</t>
+          <t>Materials Science and Engineering</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5.07 Lakhs</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7450,55 +7450,1109 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Photonics Science and Engineering</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Photonics Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>5.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>VLSI Design Tools &amp; Technology</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VLSI Design Tools &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>5.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ph.D (General)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1.58 Lakhs - 5.07 Lakhs</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>3.4 Lakhs</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Postgraduation in relevant field</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>3.4 Lakhs</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Postgraduation in relevant field</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Humanities And Social Science</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Humanities And Social Science</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>3.4 Lakhs</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Postgraduation in relevant field</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Public Policy</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Public Policy</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>3.4 Lakhs</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Postgraduation in relevant field</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>MPP</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>MPP (General)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2.36 Lakhs - 5.06 Lakhs</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MBA (General)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>12.4 Lakhs - 14.06 Lakhs</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>12.4 Lakhs - 14.06 Lakhs</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Graduation with 60%+</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Telecommunication Systems Management</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Telecommunication Systems Management</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>12.4 Lakhs - 14.06 Lakhs</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Graduation with 60%+</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>B.Des</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>B.Des (General)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>11.74 Lakhs</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>4 Years</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>UCEED</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>M.Des</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>M.Des (General)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2.76 Lakhs</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>CEED</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Executive Programme</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Executive Programme (General)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1.2 Lakhs - 1.79 Lakhs</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>EMBA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>EMBA (General)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>16.32 Lakhs - 18 Lakhs</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
           <t>Executive Programme (CEP)</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Executive Management Program in Strategic Management</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Executive Management Program in Strategic Management</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Executive Programme (CEP)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Executive Management Program in Human Resource Strategic Management</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Executive Management Program in Human Resource Strategic Management</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Executive Programme (CEP)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
         <is>
           <t>Executive Program in Robotics</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>Executive Program in Robotics</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>Part Time</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
         <is>
           <t>PG</t>
         </is>
@@ -7652,12 +8706,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2,00,00,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25,82,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -7692,7 +8746,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -7731,10 +8785,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CD Rank #1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2025</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
